--- a/test_data/RegBriefings/RegBriefings Preferences/RegBriefings Preferences_Test_Cases.xlsx
+++ b/test_data/RegBriefings/RegBriefings Preferences/RegBriefings Preferences_Test_Cases.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>All 3 Briefs checkboxes correctly reported their real state: {'World Tax Brief': False, 'Transfer Pricing Brief': False, 'Tax Treaty Brief': True}.</t>
+          <t>All 3 Briefs checkboxes correctly reported their real state: {'World Tax Brief': True, 'Transfer Pricing Brief': True, 'Tax Treaty Brief': True}.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>The 'Australia' jurisdiction checkbox was correctly present (checked=False).</t>
+          <t>The 'Australia' jurisdiction checkbox was correctly present (checked=True).</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
